--- a/results/pruebas_inicial_integrall/abundancia_pc_especie.xlsx
+++ b/results/pruebas_inicial_integrall/abundancia_pc_especie.xlsx
@@ -4144,6 +4144,9 @@
   </sheetPr>
   <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col min="11" max="11" width="27.4375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
